--- a/stock-memory/data/stockmemory.xlsx
+++ b/stock-memory/data/stockmemory.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +55,14 @@
   </si>
   <si>
     <t>메모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성전자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +70,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +95,14 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -116,11 +135,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -129,6 +163,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -403,8 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -432,8 +476,273 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5">
+        <v>198000</v>
+      </c>
+      <c r="F2" s="5">
+        <v>200</v>
+      </c>
+      <c r="G2" s="5">
+        <v>4859000</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/stock-memory/data/stockmemory.xlsx
+++ b/stock-memory/data/stockmemory.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -501,23 +501,51 @@
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="A3" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5">
+        <v>198000</v>
+      </c>
+      <c r="F3" s="5">
+        <v>200</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4859000</v>
+      </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="A4" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>198000</v>
+      </c>
+      <c r="F4" s="5">
+        <v>200</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4859000</v>
+      </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">

--- a/stock-memory/data/stockmemory.xlsx
+++ b/stock-memory/data/stockmemory.xlsx
@@ -24,45 +24,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+  <si>
+    <t>선택</t>
+  </si>
   <si>
     <t>날짜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>종목명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>체결 단가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>수수료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>정산금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>메모</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매수</t>
   </si>
   <si>
     <t>삼성전자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>매수</t>
+    <t>하이닉스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -70,10 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="#,##0_ "/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,36 +84,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -135,15 +107,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -151,11 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,331 +405,244 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="b">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
         <v>46063</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5">
-        <v>198000</v>
-      </c>
-      <c r="F2" s="5">
-        <v>200</v>
-      </c>
-      <c r="G2" s="5">
-        <v>4859000</v>
-      </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46063</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>65</v>
+      </c>
+      <c r="G2">
+        <v>564</v>
+      </c>
+      <c r="H2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46064</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
-        <v>4</v>
-      </c>
-      <c r="E3" s="5">
-        <v>198000</v>
-      </c>
-      <c r="F3" s="5">
-        <v>200</v>
-      </c>
-      <c r="G3" s="5">
-        <v>4859000</v>
-      </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46063</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
-        <v>6</v>
-      </c>
-      <c r="E4" s="5">
-        <v>198000</v>
-      </c>
-      <c r="F4" s="5">
-        <v>200</v>
-      </c>
-      <c r="G4" s="5">
-        <v>4859000</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="E3">
+        <v>46</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>41854</v>
+      </c>
+      <c r="H3">
+        <v>21854</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
